--- a/scripts/Quality_parameters.xlsx
+++ b/scripts/Quality_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daan\Documents\GitHub\Website_Open_Topography_EU\scripts\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/localadmin/Repos/Website_Open_Topography_EU/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABD9B82-16F6-4DFC-AF1F-61F84C46596A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF5230D-0800-5A41-AD39-C9BE0B93F804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality_parameters_v12032026" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2469" uniqueCount="790">
   <si>
     <t>ADM</t>
   </si>
@@ -1426,9 +1426,6 @@
   </si>
   <si>
     <t>QALIDAR</t>
-  </si>
-  <si>
-    <t>Swiss</t>
   </si>
   <si>
     <t>Le Locle</t>
@@ -2715,7 +2712,7 @@
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2909,10 +2906,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Goed" xfId="1" builtinId="26"/>
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="3" builtinId="8"/>
-    <cellStyle name="Ongeldig" xfId="2" builtinId="27"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3245,34 +3242,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E736EA-B957-4F0A-8B9F-9843A7BBC402}">
   <dimension ref="A1:BK154"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" customWidth="1"/>
-    <col min="9" max="9" width="27.28515625" customWidth="1"/>
-    <col min="10" max="13" width="39.7109375" customWidth="1"/>
-    <col min="15" max="17" width="12.5703125" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.33203125" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" customWidth="1"/>
+    <col min="10" max="13" width="39.6640625" customWidth="1"/>
+    <col min="15" max="17" width="12.5" customWidth="1"/>
+    <col min="19" max="19" width="12.5" customWidth="1"/>
     <col min="20" max="21" width="12" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.42578125" customWidth="1"/>
+    <col min="23" max="23" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5" customWidth="1"/>
     <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.28515625" customWidth="1"/>
+    <col min="26" max="26" width="9.33203125" customWidth="1"/>
     <col min="28" max="28" width="10" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="119.42578125" customWidth="1"/>
-    <col min="33" max="33" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="27.7109375" customWidth="1"/>
-    <col min="36" max="36" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="119.5" customWidth="1"/>
+    <col min="33" max="33" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="27.6640625" customWidth="1"/>
+    <col min="36" max="36" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -3295,10 +3292,10 @@
         <v>322</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>3</v>
@@ -3364,7 +3361,7 @@
         <v>363</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AF1" s="1" t="s">
         <v>364</v>
@@ -3376,7 +3373,7 @@
         <v>295</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AJ1" s="26" t="s">
         <v>278</v>
@@ -3439,7 +3436,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>17</v>
       </c>
@@ -3493,7 +3490,7 @@
       <c r="BA2" s="22"/>
       <c r="BB2" s="22"/>
     </row>
-    <row r="3" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
@@ -3547,7 +3544,7 @@
       <c r="BA3" s="22"/>
       <c r="BB3" s="22"/>
     </row>
-    <row r="4" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
@@ -3611,7 +3608,7 @@
       <c r="BA4" s="22"/>
       <c r="BB4" s="22"/>
     </row>
-    <row r="5" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -3631,7 +3628,7 @@
         <v>315</v>
       </c>
       <c r="H5" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I5" s="4">
         <v>0</v>
@@ -3689,7 +3686,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3709,7 +3706,7 @@
         <v>315</v>
       </c>
       <c r="H6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -3767,7 +3764,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:55" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -3787,7 +3784,7 @@
         <v>315</v>
       </c>
       <c r="H7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I7" s="4">
         <v>2</v>
@@ -3845,7 +3842,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
@@ -3900,7 +3897,7 @@
       <c r="BA8" s="22"/>
       <c r="BB8" s="22"/>
     </row>
-    <row r="9" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
@@ -3955,7 +3952,7 @@
       <c r="BA9" s="22"/>
       <c r="BB9" s="22"/>
     </row>
-    <row r="10" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -3972,7 +3969,7 @@
         <v>336</v>
       </c>
       <c r="H10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I10" s="4">
         <v>2</v>
@@ -4039,7 +4036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -4059,7 +4056,7 @@
         <v>315</v>
       </c>
       <c r="H11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -4135,7 +4132,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -4155,7 +4152,7 @@
         <v>315</v>
       </c>
       <c r="H12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I12" s="4">
         <v>2</v>
@@ -4228,7 +4225,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -4245,7 +4242,7 @@
         <v>315</v>
       </c>
       <c r="H13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -4301,7 +4298,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -4318,7 +4315,7 @@
         <v>315</v>
       </c>
       <c r="H14" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I14">
         <v>2</v>
@@ -4373,7 +4370,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:55" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:55" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -4393,7 +4390,7 @@
         <v>315</v>
       </c>
       <c r="H15" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -4460,7 +4457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:55" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>43</v>
       </c>
@@ -4513,7 +4510,7 @@
       <c r="BA16" s="22"/>
       <c r="BB16" s="22"/>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -4527,7 +4524,7 @@
         <v>44</v>
       </c>
       <c r="H17" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -4573,7 +4570,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>46</v>
       </c>
@@ -4621,7 +4618,7 @@
       <c r="BA18" s="22"/>
       <c r="BB18" s="22"/>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -4650,7 +4647,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>49</v>
       </c>
@@ -4670,7 +4667,7 @@
         <v>324</v>
       </c>
       <c r="H20" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -4711,7 +4708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -4725,13 +4722,13 @@
         <v>53</v>
       </c>
       <c r="F21" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>323</v>
       </c>
       <c r="H21" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -4813,7 +4810,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -4827,13 +4824,13 @@
         <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>323</v>
       </c>
       <c r="H22" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4894,7 +4891,7 @@
         <v>368</v>
       </c>
       <c r="AE22" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AF22" t="s">
         <v>367</v>
@@ -4916,7 +4913,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -4930,13 +4927,13 @@
         <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G23" t="s">
         <v>324</v>
       </c>
       <c r="H23" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I23">
         <v>1</v>
@@ -4982,7 +4979,7 @@
         <v>325</v>
       </c>
       <c r="AE23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="AF23" s="6" t="s">
         <v>326</v>
@@ -5018,7 +5015,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="24" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>57</v>
       </c>
@@ -5066,7 +5063,7 @@
       <c r="BA24" s="22"/>
       <c r="BB24" s="22"/>
     </row>
-    <row r="25" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>58</v>
       </c>
@@ -5114,7 +5111,7 @@
       <c r="BA25" s="22"/>
       <c r="BB25" s="22"/>
     </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -5128,10 +5125,10 @@
         <v>59</v>
       </c>
       <c r="E26" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F26" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -5176,7 +5173,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:54" s="4" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>63</v>
       </c>
@@ -5190,7 +5187,7 @@
         <v>63</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G27" s="31" t="s">
         <v>315</v>
@@ -5226,13 +5223,13 @@
         <v>2014</v>
       </c>
       <c r="AD27" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="AE27" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="AE27" s="4" t="s">
+      <c r="AG27" s="4" t="s">
         <v>771</v>
-      </c>
-      <c r="AG27" s="4" t="s">
-        <v>772</v>
       </c>
       <c r="AJ27" s="22"/>
       <c r="AK27" s="22"/>
@@ -5254,7 +5251,7 @@
       <c r="BA27" s="22"/>
       <c r="BB27" s="22"/>
     </row>
-    <row r="28" spans="1:54" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:54" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -5268,7 +5265,7 @@
         <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G28" t="s">
         <v>315</v>
@@ -5316,7 +5313,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:54" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:54" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -5330,7 +5327,7 @@
         <v>64</v>
       </c>
       <c r="F29" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G29" t="s">
         <v>315</v>
@@ -5378,7 +5375,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:54" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:54" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>68</v>
       </c>
@@ -5392,7 +5389,7 @@
         <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G30" t="s">
         <v>315</v>
@@ -5457,13 +5454,13 @@
         <v>275</v>
       </c>
       <c r="AL30" s="27" t="s">
+        <v>511</v>
+      </c>
+      <c r="AM30" s="27" t="s">
         <v>512</v>
       </c>
-      <c r="AM30" s="27" t="s">
+      <c r="AN30" t="s">
         <v>513</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>514</v>
       </c>
       <c r="AO30" s="27"/>
       <c r="AP30" t="s">
@@ -5481,10 +5478,10 @@
         <v>277</v>
       </c>
       <c r="BB30" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="31" spans="1:54" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -5498,7 +5495,7 @@
         <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -5563,17 +5560,17 @@
         <v>278</v>
       </c>
       <c r="AK31" s="27" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AL31" s="27"/>
       <c r="AN31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AP31" t="s">
         <v>279</v>
       </c>
       <c r="AQ31" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AR31" t="s">
         <v>270</v>
@@ -5581,13 +5578,13 @@
       <c r="AW31" s="27"/>
       <c r="AX31" s="27"/>
       <c r="AY31" t="s">
+        <v>518</v>
+      </c>
+      <c r="BB31" t="s">
         <v>519</v>
       </c>
-      <c r="BB31" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="32" spans="1:54" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:54" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -5601,7 +5598,7 @@
         <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -5666,17 +5663,17 @@
         <v>278</v>
       </c>
       <c r="AK32" s="27" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AL32" s="27"/>
       <c r="AN32" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AP32" t="s">
         <v>279</v>
       </c>
       <c r="AQ32" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AR32" t="s">
         <v>270</v>
@@ -5684,13 +5681,13 @@
       <c r="AW32" s="27"/>
       <c r="AX32" s="27"/>
       <c r="AY32" t="s">
+        <v>518</v>
+      </c>
+      <c r="BB32" t="s">
         <v>519</v>
       </c>
-      <c r="BB32" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="33" spans="1:63" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:63" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -5704,7 +5701,7 @@
         <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -5769,17 +5766,17 @@
         <v>278</v>
       </c>
       <c r="AK33" s="27" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AL33" s="27"/>
       <c r="AN33" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AP33" t="s">
         <v>279</v>
       </c>
       <c r="AQ33" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AR33" t="s">
         <v>270</v>
@@ -5787,13 +5784,13 @@
       <c r="AW33" s="27"/>
       <c r="AX33" s="27"/>
       <c r="AY33" t="s">
+        <v>518</v>
+      </c>
+      <c r="BB33" t="s">
         <v>519</v>
       </c>
-      <c r="BB33" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:63" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:63" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>73</v>
       </c>
@@ -5807,7 +5804,7 @@
         <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -5872,17 +5869,17 @@
         <v>278</v>
       </c>
       <c r="AK34" s="27" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AL34" s="27"/>
       <c r="AN34" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AP34" t="s">
         <v>279</v>
       </c>
       <c r="AQ34" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AR34" t="s">
         <v>270</v>
@@ -5890,13 +5887,13 @@
       <c r="AW34" s="27"/>
       <c r="AX34" s="27"/>
       <c r="AY34" t="s">
+        <v>518</v>
+      </c>
+      <c r="BB34" t="s">
         <v>519</v>
       </c>
-      <c r="BB34" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>73</v>
       </c>
@@ -5910,7 +5907,7 @@
         <v>150</v>
       </c>
       <c r="H35" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I35">
         <v>1</v>
@@ -5919,28 +5916,28 @@
         <v>278</v>
       </c>
       <c r="AK35" t="s">
+        <v>515</v>
+      </c>
+      <c r="AN35" t="s">
         <v>516</v>
-      </c>
-      <c r="AN35" t="s">
-        <v>517</v>
       </c>
       <c r="AP35" t="s">
         <v>279</v>
       </c>
       <c r="AQ35" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AR35" t="s">
         <v>270</v>
       </c>
       <c r="AY35" t="s">
+        <v>518</v>
+      </c>
+      <c r="BB35" t="s">
         <v>519</v>
       </c>
-      <c r="BB35" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="36" spans="1:63" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:63" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -5954,7 +5951,7 @@
         <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -6022,40 +6019,40 @@
         <v>280</v>
       </c>
       <c r="AM36" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="AN36" t="s">
         <v>521</v>
       </c>
-      <c r="AN36" t="s">
+      <c r="AQ36" t="s">
         <v>522</v>
       </c>
-      <c r="AQ36" t="s">
+      <c r="AR36" s="27" t="s">
         <v>523</v>
       </c>
-      <c r="AR36" s="27" t="s">
+      <c r="AS36" t="s">
         <v>524</v>
       </c>
-      <c r="AS36" t="s">
+      <c r="AU36" s="27" t="s">
         <v>525</v>
       </c>
-      <c r="AU36" s="27" t="s">
+      <c r="AV36" s="27" t="s">
         <v>526</v>
       </c>
-      <c r="AV36" s="27" t="s">
+      <c r="AW36" s="27" t="s">
         <v>527</v>
       </c>
-      <c r="AW36" s="27" t="s">
+      <c r="AX36" t="s">
         <v>528</v>
       </c>
-      <c r="AX36" t="s">
+      <c r="AY36" t="s">
         <v>529</v>
       </c>
-      <c r="AY36" t="s">
+      <c r="BB36" t="s">
         <v>530</v>
       </c>
-      <c r="BB36" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="37" spans="1:63" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:63" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>78</v>
       </c>
@@ -6069,7 +6066,7 @@
         <v>78</v>
       </c>
       <c r="F37" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -6137,40 +6134,40 @@
         <v>280</v>
       </c>
       <c r="AM37" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="AN37" t="s">
         <v>521</v>
       </c>
-      <c r="AN37" t="s">
+      <c r="AQ37" t="s">
         <v>522</v>
       </c>
-      <c r="AQ37" t="s">
+      <c r="AR37" s="27" t="s">
         <v>523</v>
       </c>
-      <c r="AR37" s="27" t="s">
+      <c r="AS37" t="s">
         <v>524</v>
       </c>
-      <c r="AS37" t="s">
+      <c r="AU37" s="27" t="s">
         <v>525</v>
       </c>
-      <c r="AU37" s="27" t="s">
+      <c r="AV37" s="27" t="s">
         <v>526</v>
       </c>
-      <c r="AV37" s="27" t="s">
+      <c r="AW37" s="27" t="s">
         <v>527</v>
       </c>
-      <c r="AW37" s="27" t="s">
+      <c r="AX37" t="s">
         <v>528</v>
       </c>
-      <c r="AX37" t="s">
+      <c r="AY37" t="s">
         <v>529</v>
       </c>
-      <c r="AY37" t="s">
+      <c r="BB37" t="s">
         <v>530</v>
       </c>
-      <c r="BB37" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="38" spans="1:63" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:63" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -6184,7 +6181,7 @@
         <v>83</v>
       </c>
       <c r="F38" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -6262,16 +6259,16 @@
         <v>270</v>
       </c>
       <c r="AY38" t="s">
+        <v>531</v>
+      </c>
+      <c r="BB38" t="s">
         <v>532</v>
-      </c>
-      <c r="BB38" t="s">
-        <v>533</v>
       </c>
       <c r="BH38" s="2"/>
       <c r="BJ38" s="3"/>
       <c r="BK38" s="2"/>
     </row>
-    <row r="39" spans="1:63" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:63" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>83</v>
       </c>
@@ -6285,7 +6282,7 @@
         <v>83</v>
       </c>
       <c r="F39" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -6363,16 +6360,16 @@
         <v>270</v>
       </c>
       <c r="AY39" t="s">
+        <v>531</v>
+      </c>
+      <c r="BB39" t="s">
         <v>532</v>
-      </c>
-      <c r="BB39" t="s">
-        <v>533</v>
       </c>
       <c r="BH39" s="2"/>
       <c r="BJ39" s="3"/>
       <c r="BK39" s="2"/>
     </row>
-    <row r="40" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>88</v>
       </c>
@@ -6386,7 +6383,7 @@
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -6458,7 +6455,7 @@
         <v>279</v>
       </c>
       <c r="AQ40" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AR40" t="s">
         <v>270</v>
@@ -6467,10 +6464,10 @@
         <v>277</v>
       </c>
       <c r="BB40" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="41" spans="1:63" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:63" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -6484,13 +6481,13 @@
         <v>92</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H41" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -6541,7 +6538,7 @@
       <c r="BJ41" s="9"/>
       <c r="BK41" s="2"/>
     </row>
-    <row r="42" spans="1:63" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:63" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -6555,13 +6552,13 @@
         <v>94</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H42" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -6606,7 +6603,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="1:63" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:63" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -6620,16 +6617,16 @@
         <v>95</v>
       </c>
       <c r="E43" s="31" t="s">
+        <v>772</v>
+      </c>
+      <c r="F43" t="s">
         <v>773</v>
-      </c>
-      <c r="F43" t="s">
-        <v>774</v>
       </c>
       <c r="G43" t="s">
         <v>315</v>
       </c>
       <c r="H43" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I43">
         <v>1</v>
@@ -6683,7 +6680,7 @@
         <v>2024</v>
       </c>
       <c r="AE43" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AF43" t="s">
         <v>96</v>
@@ -6701,10 +6698,10 @@
         <v>279</v>
       </c>
       <c r="BB43" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="44" spans="1:63" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="44" spans="1:63" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -6718,16 +6715,16 @@
         <v>97</v>
       </c>
       <c r="E44" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F44" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H44" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I44">
         <v>1</v>
@@ -6775,7 +6772,7 @@
         <v>2021</v>
       </c>
       <c r="AD44" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AF44" s="6" t="s">
         <v>98</v>
@@ -6799,10 +6796,10 @@
         <v>282</v>
       </c>
       <c r="AQ44" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="45" spans="1:63" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="45" spans="1:63" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>99</v>
       </c>
@@ -6816,13 +6813,13 @@
         <v>99</v>
       </c>
       <c r="E45" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G45" t="s">
         <v>315</v>
       </c>
       <c r="H45" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -6875,13 +6872,13 @@
       </c>
       <c r="AE45" s="6"/>
       <c r="AF45" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AG45" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46" spans="1:63" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:63" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>101</v>
       </c>
@@ -6895,13 +6892,13 @@
         <v>101</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H46" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I46">
         <v>1</v>
@@ -6953,13 +6950,13 @@
       </c>
       <c r="AE46" s="6"/>
       <c r="AF46" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AG46" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="47" spans="1:63" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>103</v>
       </c>
@@ -6976,7 +6973,7 @@
         <v>320</v>
       </c>
       <c r="H47" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I47">
         <v>1</v>
@@ -7024,11 +7021,11 @@
         <v>2021</v>
       </c>
       <c r="AD47" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AE47" s="6"/>
       <c r="AF47" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AG47" t="s">
         <v>37</v>
@@ -7040,22 +7037,22 @@
         <v>275</v>
       </c>
       <c r="AL47" t="s">
+        <v>537</v>
+      </c>
+      <c r="AM47" t="s">
         <v>538</v>
       </c>
-      <c r="AM47" t="s">
+      <c r="AN47" t="s">
         <v>539</v>
-      </c>
-      <c r="AN47" t="s">
-        <v>540</v>
       </c>
       <c r="AP47" t="s">
         <v>279</v>
       </c>
       <c r="AQ47" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="48" spans="1:63" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="48" spans="1:63" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>104</v>
       </c>
@@ -7069,16 +7066,16 @@
         <v>104</v>
       </c>
       <c r="E48" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F48" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G48" t="s">
         <v>315</v>
       </c>
       <c r="H48" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -7130,13 +7127,13 @@
       </c>
       <c r="AE48" s="6"/>
       <c r="AF48" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AG48" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>106</v>
       </c>
@@ -7153,7 +7150,7 @@
         <v>320</v>
       </c>
       <c r="H49" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -7204,10 +7201,10 @@
         <v>108</v>
       </c>
       <c r="AJ49" t="s">
+        <v>541</v>
+      </c>
+      <c r="AK49" t="s">
         <v>542</v>
-      </c>
-      <c r="AK49" t="s">
-        <v>543</v>
       </c>
       <c r="AR49" t="s">
         <v>284</v>
@@ -7219,13 +7216,13 @@
         <v>286</v>
       </c>
       <c r="BA49" t="s">
+        <v>543</v>
+      </c>
+      <c r="BB49" t="s">
         <v>544</v>
       </c>
-      <c r="BB49" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="50" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>109</v>
       </c>
@@ -7239,13 +7236,13 @@
         <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H50" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I50">
         <v>1</v>
@@ -7296,7 +7293,7 @@
         <v>2024</v>
       </c>
       <c r="AD50" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AE50" s="6"/>
       <c r="AF50" s="17" t="s">
@@ -7318,13 +7315,13 @@
         <v>270</v>
       </c>
       <c r="AV50" t="s">
+        <v>545</v>
+      </c>
+      <c r="BB50" t="s">
         <v>546</v>
       </c>
-      <c r="BB50" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="51" spans="1:54" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:54" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>111</v>
       </c>
@@ -7338,13 +7335,13 @@
         <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G51" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H51" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -7389,7 +7386,7 @@
         <v>2025</v>
       </c>
       <c r="AD51" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AE51" s="6"/>
       <c r="AF51" s="6" t="s">
@@ -7399,7 +7396,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:54" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:54" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>113</v>
       </c>
@@ -7413,16 +7410,16 @@
         <v>113</v>
       </c>
       <c r="E52" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F52" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G52" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H52" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -7471,13 +7468,13 @@
       </c>
       <c r="AE52" s="6"/>
       <c r="AF52" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AG52" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>115</v>
       </c>
@@ -7491,13 +7488,13 @@
         <v>115</v>
       </c>
       <c r="E53" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G53" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H53" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I53">
         <v>1</v>
@@ -7545,17 +7542,17 @@
         <v>2023</v>
       </c>
       <c r="AD53" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AE53" s="6"/>
       <c r="AF53" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AG53" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="54" spans="1:54" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:54" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -7569,16 +7566,16 @@
         <v>117</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G54" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H54" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I54">
         <v>1</v>
@@ -7605,7 +7602,7 @@
         <v>1</v>
       </c>
       <c r="S54" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="T54">
         <v>4</v>
@@ -7623,17 +7620,17 @@
         <v>geen data</v>
       </c>
       <c r="AD54" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AE54" s="6"/>
       <c r="AF54" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AG54" s="13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:54" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:54" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>118</v>
       </c>
@@ -7647,13 +7644,13 @@
         <v>118</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G55" s="6" t="s">
         <v>320</v>
       </c>
       <c r="H55" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -7705,13 +7702,13 @@
       </c>
       <c r="AE55" s="6"/>
       <c r="AF55" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AG55" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>120</v>
       </c>
@@ -7725,7 +7722,7 @@
         <v>120</v>
       </c>
       <c r="H56" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -7788,17 +7785,17 @@
         <v>2013</v>
       </c>
       <c r="AD56" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AE56" s="6"/>
       <c r="AF56" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG56" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -7812,7 +7809,7 @@
         <v>120</v>
       </c>
       <c r="H57" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I57">
         <v>2</v>
@@ -7875,17 +7872,17 @@
         <v>2019</v>
       </c>
       <c r="AD57" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AE57" s="6"/>
       <c r="AF57" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG57" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:54" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>120</v>
       </c>
@@ -7899,7 +7896,7 @@
         <v>120</v>
       </c>
       <c r="H58" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -7962,17 +7959,17 @@
         <v>2025</v>
       </c>
       <c r="AD58" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AE58" s="6"/>
       <c r="AF58" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AG58" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="59" spans="1:54" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:54" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>121</v>
       </c>
@@ -8008,12 +8005,12 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:54" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:54" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>123</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C60" t="s">
         <v>121</v>
@@ -8022,7 +8019,7 @@
         <v>123</v>
       </c>
       <c r="H60" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -8067,7 +8064,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="61" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>128</v>
       </c>
@@ -8115,7 +8112,7 @@
       <c r="BA61" s="22"/>
       <c r="BB61" s="22"/>
     </row>
-    <row r="62" spans="1:54" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:54" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>129</v>
       </c>
@@ -8129,10 +8126,10 @@
         <v>129</v>
       </c>
       <c r="F62" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I62" s="5">
         <v>1</v>
@@ -8189,7 +8186,7 @@
       <c r="BA62" s="28"/>
       <c r="BB62" s="28"/>
     </row>
-    <row r="63" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -8203,10 +8200,10 @@
         <v>132</v>
       </c>
       <c r="E63" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F63" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -8248,12 +8245,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="64" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>132</v>
       </c>
       <c r="B64" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C64" t="s">
         <v>132</v>
@@ -8262,18 +8259,18 @@
         <v>292</v>
       </c>
       <c r="F64" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H64" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B65" s="4">
         <v>1</v>
@@ -8282,10 +8279,10 @@
         <v>135</v>
       </c>
       <c r="D65" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H65" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I65">
         <v>2</v>
@@ -8294,7 +8291,7 @@
         <v>25</v>
       </c>
       <c r="K65" s="32" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M65" t="s">
         <v>39</v>
@@ -8312,13 +8309,13 @@
         <v>0.3</v>
       </c>
       <c r="AD65" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AE65" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="66" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="66" spans="1:54" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>137</v>
       </c>
@@ -8334,7 +8331,7 @@
       <c r="E66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I66" s="2"/>
       <c r="J66" t="s">
@@ -8375,13 +8372,13 @@
       </c>
       <c r="AE66" s="6"/>
       <c r="AF66" s="6" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AG66" s="13" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="67" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>140</v>
       </c>
@@ -8397,7 +8394,7 @@
       <c r="E67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I67" s="2"/>
       <c r="J67" t="s">
@@ -8431,7 +8428,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="68" spans="1:54" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:54" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>142</v>
       </c>
@@ -8447,7 +8444,7 @@
       <c r="E68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" t="s">
@@ -8478,13 +8475,13 @@
         <v>2010</v>
       </c>
       <c r="AF68" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AG68" s="13" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="69" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="69" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>135</v>
       </c>
@@ -8498,7 +8495,7 @@
         <v>135</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="J69" t="s">
         <v>25</v>
@@ -8536,14 +8533,14 @@
         <v>2026</v>
       </c>
       <c r="AB69" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AD69" s="20" t="s">
         <v>136</v>
       </c>
       <c r="AE69" s="20"/>
       <c r="AF69" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="AG69" s="4" t="s">
         <v>143</v>
@@ -8568,7 +8565,7 @@
       <c r="BA69" s="22"/>
       <c r="BB69" s="22"/>
     </row>
-    <row r="70" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>144</v>
       </c>
@@ -8616,7 +8613,7 @@
       <c r="BA70" s="22"/>
       <c r="BB70" s="22"/>
     </row>
-    <row r="71" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>145</v>
       </c>
@@ -8630,13 +8627,13 @@
         <v>145</v>
       </c>
       <c r="E71" t="s">
+        <v>762</v>
+      </c>
+      <c r="F71" t="s">
+        <v>596</v>
+      </c>
+      <c r="G71" t="s">
         <v>763</v>
-      </c>
-      <c r="F71" t="s">
-        <v>597</v>
-      </c>
-      <c r="G71" t="s">
-        <v>764</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -8690,7 +8687,7 @@
         <v>2019</v>
       </c>
       <c r="AE71" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AF71" t="s">
         <v>148</v>
@@ -8717,12 +8714,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="72" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>150</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C72" t="s">
         <v>150</v>
@@ -8731,10 +8728,10 @@
         <v>150</v>
       </c>
       <c r="F72" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H72" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I72">
         <v>1</v>
@@ -8775,7 +8772,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="73" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>153</v>
       </c>
@@ -8789,10 +8786,10 @@
         <v>153</v>
       </c>
       <c r="F73" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H73" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -8834,7 +8831,7 @@
         <v>154</v>
       </c>
       <c r="AJ73" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK73" t="s">
         <v>275</v>
@@ -8849,10 +8846,10 @@
         <v>270</v>
       </c>
       <c r="AY73" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="74" spans="1:54" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="74" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>155</v>
       </c>
@@ -8866,13 +8863,13 @@
         <v>155</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F74" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -8893,7 +8890,7 @@
         <v>26</v>
       </c>
       <c r="N74" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="O74" t="s">
         <v>35</v>
@@ -8929,10 +8926,10 @@
         <v>2022</v>
       </c>
       <c r="AD74" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AF74" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AG74" s="2" t="s">
         <v>157</v>
@@ -8962,10 +8959,10 @@
       </c>
       <c r="AR74" s="27"/>
       <c r="BB74" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="75" spans="1:54" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="75" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>155</v>
       </c>
@@ -8979,10 +8976,10 @@
         <v>155</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F75" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -9033,10 +9030,10 @@
         <v>2025</v>
       </c>
       <c r="AD75" t="s">
+        <v>784</v>
+      </c>
+      <c r="AF75" s="8" t="s">
         <v>785</v>
-      </c>
-      <c r="AF75" s="8" t="s">
-        <v>786</v>
       </c>
       <c r="AG75" s="2" t="s">
         <v>157</v>
@@ -9066,10 +9063,10 @@
       </c>
       <c r="AR75" s="27"/>
       <c r="BB75" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="76" spans="1:54" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="76" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>158</v>
       </c>
@@ -9083,7 +9080,7 @@
         <v>158</v>
       </c>
       <c r="F76" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -9155,7 +9152,7 @@
         <v>279</v>
       </c>
       <c r="AQ76" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AR76" t="s">
         <v>270</v>
@@ -9171,7 +9168,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="77" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>162</v>
       </c>
@@ -9185,7 +9182,7 @@
         <v>162</v>
       </c>
       <c r="F77" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -9260,7 +9257,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="78" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>166</v>
       </c>
@@ -9308,7 +9305,7 @@
       <c r="BA78" s="22"/>
       <c r="BB78" s="22"/>
     </row>
-    <row r="79" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>167</v>
       </c>
@@ -9356,7 +9353,7 @@
       <c r="BA79" s="22"/>
       <c r="BB79" s="22"/>
     </row>
-    <row r="80" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>168</v>
       </c>
@@ -9404,7 +9401,7 @@
       <c r="BA80" s="22"/>
       <c r="BB80" s="22"/>
     </row>
-    <row r="81" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>169</v>
       </c>
@@ -9445,7 +9442,7 @@
         <v>338</v>
       </c>
       <c r="N81" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O81" t="s">
         <v>35</v>
@@ -9493,7 +9490,7 @@
         <v>2012</v>
       </c>
       <c r="AD81" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AF81" t="s">
         <v>171</v>
@@ -9502,7 +9499,7 @@
         <v>172</v>
       </c>
       <c r="AK81" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL81" s="27"/>
       <c r="AP81" t="s">
@@ -9513,14 +9510,14 @@
       </c>
       <c r="AT81" s="27"/>
       <c r="AV81" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB81" t="s">
         <v>551</v>
       </c>
-      <c r="BB81" t="s">
-        <v>552</v>
-      </c>
       <c r="BE81" s="27"/>
     </row>
-    <row r="82" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>169</v>
       </c>
@@ -9561,7 +9558,7 @@
         <v>338</v>
       </c>
       <c r="N82" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O82" t="s">
         <v>35</v>
@@ -9609,7 +9606,7 @@
         <v>2019</v>
       </c>
       <c r="AD82" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="AF82" t="s">
         <v>171</v>
@@ -9618,7 +9615,7 @@
         <v>172</v>
       </c>
       <c r="AK82" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL82" s="27"/>
       <c r="AP82" t="s">
@@ -9629,14 +9626,14 @@
       </c>
       <c r="AT82" s="27"/>
       <c r="AV82" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB82" t="s">
         <v>551</v>
       </c>
-      <c r="BB82" t="s">
-        <v>552</v>
-      </c>
       <c r="BE82" s="27"/>
     </row>
-    <row r="83" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>169</v>
       </c>
@@ -9677,7 +9674,7 @@
         <v>338</v>
       </c>
       <c r="N83" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O83" t="s">
         <v>35</v>
@@ -9725,7 +9722,7 @@
         <v>2023</v>
       </c>
       <c r="AD83" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="AF83" t="s">
         <v>171</v>
@@ -9734,7 +9731,7 @@
         <v>172</v>
       </c>
       <c r="AK83" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL83" s="27"/>
       <c r="AP83" t="s">
@@ -9745,14 +9742,14 @@
       </c>
       <c r="AT83" s="27"/>
       <c r="AV83" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB83" t="s">
         <v>551</v>
       </c>
-      <c r="BB83" t="s">
-        <v>552</v>
-      </c>
       <c r="BE83" s="27"/>
     </row>
-    <row r="84" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>169</v>
       </c>
@@ -9793,7 +9790,7 @@
         <v>338</v>
       </c>
       <c r="N84" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O84" t="s">
         <v>35</v>
@@ -9841,7 +9838,7 @@
         <v>2024</v>
       </c>
       <c r="AD84" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="AF84" t="s">
         <v>171</v>
@@ -9850,7 +9847,7 @@
         <v>172</v>
       </c>
       <c r="AK84" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL84" s="27"/>
       <c r="AP84" t="s">
@@ -9861,14 +9858,14 @@
       </c>
       <c r="AT84" s="27"/>
       <c r="AV84" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB84" t="s">
         <v>551</v>
       </c>
-      <c r="BB84" t="s">
-        <v>552</v>
-      </c>
       <c r="BE84" s="27"/>
     </row>
-    <row r="85" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>169</v>
       </c>
@@ -9909,7 +9906,7 @@
         <v>338</v>
       </c>
       <c r="N85" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O85" t="s">
         <v>35</v>
@@ -9957,7 +9954,7 @@
         <v>2027</v>
       </c>
       <c r="AD85" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AF85" t="s">
         <v>171</v>
@@ -9966,7 +9963,7 @@
         <v>172</v>
       </c>
       <c r="AK85" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AL85" s="27"/>
       <c r="AP85" t="s">
@@ -9977,14 +9974,14 @@
       </c>
       <c r="AT85" s="27"/>
       <c r="AV85" t="s">
+        <v>550</v>
+      </c>
+      <c r="BB85" t="s">
         <v>551</v>
       </c>
-      <c r="BB85" t="s">
-        <v>552</v>
-      </c>
       <c r="BE85" s="27"/>
     </row>
-    <row r="86" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>169</v>
       </c>
@@ -10031,7 +10028,7 @@
         <v>1</v>
       </c>
       <c r="R86" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="U86">
         <v>25</v>
@@ -10055,7 +10052,7 @@
         <v>2021</v>
       </c>
       <c r="AF86" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AG86" s="15" t="s">
         <v>172</v>
@@ -10064,12 +10061,12 @@
       <c r="AT86" s="27"/>
       <c r="BE86" s="27"/>
     </row>
-    <row r="87" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>294</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C87" t="s">
         <v>169</v>
@@ -10078,7 +10075,7 @@
         <v>294</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>334</v>
@@ -10087,7 +10084,7 @@
         <v>315</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="I87" s="4">
         <v>1</v>
@@ -10123,7 +10120,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>175</v>
       </c>
@@ -10137,7 +10134,7 @@
         <v>175</v>
       </c>
       <c r="E88" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -10183,13 +10180,13 @@
       </c>
       <c r="AE88" s="6"/>
       <c r="AF88" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="AG88" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="89" spans="1:59" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:59" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>178</v>
       </c>
@@ -10203,10 +10200,10 @@
         <v>178</v>
       </c>
       <c r="E89" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F89" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -10251,13 +10248,13 @@
         <v>1</v>
       </c>
       <c r="AB89" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AD89" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AE89" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AF89" t="s">
         <v>181</v>
@@ -10269,13 +10266,13 @@
         <v>278</v>
       </c>
       <c r="AQ89" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR89" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:59" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>183</v>
       </c>
@@ -10289,10 +10286,10 @@
         <v>183</v>
       </c>
       <c r="F90" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G90" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -10344,7 +10341,7 @@
       </c>
       <c r="AC90" s="6"/>
       <c r="AD90" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AE90" s="6"/>
       <c r="AF90" s="6" t="s">
@@ -10354,31 +10351,31 @@
         <v>186</v>
       </c>
       <c r="AI90" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AK90" s="27" t="s">
         <v>275</v>
       </c>
       <c r="AL90" s="27" t="s">
+        <v>676</v>
+      </c>
+      <c r="AM90" s="27" t="s">
+        <v>675</v>
+      </c>
+      <c r="AN90" s="27" t="s">
         <v>677</v>
       </c>
-      <c r="AM90" s="27" t="s">
-        <v>676</v>
-      </c>
-      <c r="AN90" s="27" t="s">
+      <c r="AP90" t="s">
         <v>678</v>
-      </c>
-      <c r="AP90" t="s">
-        <v>679</v>
       </c>
       <c r="AQ90" t="s">
         <v>274</v>
       </c>
       <c r="BB90" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="91" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="91" spans="1:59" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -10392,10 +10389,10 @@
         <v>187</v>
       </c>
       <c r="F91" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G91" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -10425,10 +10422,10 @@
         <v>1</v>
       </c>
       <c r="R91" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="S91" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="T91">
         <v>10</v>
@@ -10455,7 +10452,7 @@
         <v>2024</v>
       </c>
       <c r="AD91" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AF91" s="7" t="s">
         <v>293</v>
@@ -10473,7 +10470,7 @@
         <v>280</v>
       </c>
       <c r="AM91" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN91" t="s">
         <v>282</v>
@@ -10489,11 +10486,11 @@
         <v>270</v>
       </c>
       <c r="BB91" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BG91" s="2"/>
     </row>
-    <row r="92" spans="1:59" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:59" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>191</v>
       </c>
@@ -10507,7 +10504,7 @@
         <v>191</v>
       </c>
       <c r="H92" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -10521,7 +10518,7 @@
       <c r="AM92" s="27"/>
       <c r="AO92" s="27"/>
     </row>
-    <row r="93" spans="1:59" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:59" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>194</v>
       </c>
@@ -10535,16 +10532,16 @@
         <v>194</v>
       </c>
       <c r="E93" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F93" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G93" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H93" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -10582,7 +10579,7 @@
         <v>2024</v>
       </c>
       <c r="AB93" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF93" t="s">
         <v>193</v>
@@ -10596,13 +10593,13 @@
         <v>278</v>
       </c>
       <c r="AK93" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL93" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM93" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN93" t="s">
         <v>282</v>
@@ -10612,19 +10609,19 @@
         <v>276</v>
       </c>
       <c r="AQ93" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR93" t="s">
         <v>270</v>
       </c>
       <c r="AY93" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB93" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="94" spans="1:59" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="94" spans="1:59" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>197</v>
       </c>
@@ -10638,16 +10635,16 @@
         <v>197</v>
       </c>
       <c r="E94" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F94" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G94" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H94" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I94">
         <v>1</v>
@@ -10685,7 +10682,7 @@
         <v>2024</v>
       </c>
       <c r="AB94" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF94" t="s">
         <v>193</v>
@@ -10699,13 +10696,13 @@
         <v>278</v>
       </c>
       <c r="AK94" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL94" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM94" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN94" t="s">
         <v>282</v>
@@ -10715,19 +10712,19 @@
         <v>276</v>
       </c>
       <c r="AQ94" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR94" t="s">
         <v>270</v>
       </c>
       <c r="AY94" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB94" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="95" spans="1:59" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="95" spans="1:59" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>199</v>
       </c>
@@ -10741,16 +10738,16 @@
         <v>199</v>
       </c>
       <c r="E95" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F95" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G95" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H95" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I95">
         <v>1</v>
@@ -10788,7 +10785,7 @@
         <v>2024</v>
       </c>
       <c r="AB95" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF95" t="s">
         <v>193</v>
@@ -10802,13 +10799,13 @@
         <v>278</v>
       </c>
       <c r="AK95" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL95" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM95" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN95" t="s">
         <v>282</v>
@@ -10818,19 +10815,19 @@
         <v>276</v>
       </c>
       <c r="AQ95" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR95" t="s">
         <v>270</v>
       </c>
       <c r="AY95" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB95" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="96" spans="1:59" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="96" spans="1:59" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>201</v>
       </c>
@@ -10844,16 +10841,16 @@
         <v>201</v>
       </c>
       <c r="E96" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F96" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G96" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H96" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I96">
         <v>1</v>
@@ -10891,7 +10888,7 @@
         <v>2024</v>
       </c>
       <c r="AB96" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF96" t="s">
         <v>193</v>
@@ -10905,13 +10902,13 @@
         <v>278</v>
       </c>
       <c r="AK96" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL96" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM96" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN96" t="s">
         <v>282</v>
@@ -10921,19 +10918,19 @@
         <v>276</v>
       </c>
       <c r="AQ96" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR96" t="s">
         <v>270</v>
       </c>
       <c r="AY96" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB96" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="97" spans="1:54" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="97" spans="1:54" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>203</v>
       </c>
@@ -10947,16 +10944,16 @@
         <v>203</v>
       </c>
       <c r="E97" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F97" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G97" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H97" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -10994,7 +10991,7 @@
         <v>2024</v>
       </c>
       <c r="AB97" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF97" t="s">
         <v>193</v>
@@ -11008,13 +11005,13 @@
         <v>278</v>
       </c>
       <c r="AK97" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL97" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM97" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN97" t="s">
         <v>282</v>
@@ -11024,19 +11021,19 @@
         <v>276</v>
       </c>
       <c r="AQ97" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR97" t="s">
         <v>270</v>
       </c>
       <c r="AY97" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB97" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="98" spans="1:54" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="98" spans="1:54" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>205</v>
       </c>
@@ -11050,16 +11047,16 @@
         <v>205</v>
       </c>
       <c r="E98" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F98" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G98" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H98" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -11097,7 +11094,7 @@
         <v>2024</v>
       </c>
       <c r="AB98" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF98" t="s">
         <v>193</v>
@@ -11111,13 +11108,13 @@
         <v>278</v>
       </c>
       <c r="AK98" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL98" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM98" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN98" t="s">
         <v>282</v>
@@ -11126,19 +11123,19 @@
         <v>276</v>
       </c>
       <c r="AQ98" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR98" t="s">
         <v>270</v>
       </c>
       <c r="AY98" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB98" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="99" spans="1:54" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="99" spans="1:54" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>207</v>
       </c>
@@ -11152,16 +11149,16 @@
         <v>207</v>
       </c>
       <c r="E99" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F99" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G99" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H99" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I99">
         <v>1</v>
@@ -11199,7 +11196,7 @@
         <v>2024</v>
       </c>
       <c r="AB99" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF99" t="s">
         <v>193</v>
@@ -11213,13 +11210,13 @@
         <v>278</v>
       </c>
       <c r="AK99" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL99" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM99" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN99" t="s">
         <v>282</v>
@@ -11229,19 +11226,19 @@
         <v>276</v>
       </c>
       <c r="AQ99" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR99" t="s">
         <v>270</v>
       </c>
       <c r="AY99" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB99" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="100" spans="1:54" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="100" spans="1:54" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>209</v>
       </c>
@@ -11255,16 +11252,16 @@
         <v>209</v>
       </c>
       <c r="E100" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F100" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G100" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H100" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -11302,7 +11299,7 @@
         <v>2024</v>
       </c>
       <c r="AB100" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF100" t="s">
         <v>193</v>
@@ -11316,13 +11313,13 @@
         <v>278</v>
       </c>
       <c r="AK100" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL100" s="27" t="s">
         <v>280</v>
       </c>
       <c r="AM100" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AN100" t="s">
         <v>282</v>
@@ -11332,19 +11329,19 @@
         <v>276</v>
       </c>
       <c r="AQ100" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AR100" t="s">
         <v>270</v>
       </c>
       <c r="AY100" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB100" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="101" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="101" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>211</v>
       </c>
@@ -11358,16 +11355,16 @@
         <v>211</v>
       </c>
       <c r="E101" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F101" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G101" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H101" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -11413,7 +11410,7 @@
         <v>278</v>
       </c>
       <c r="AK101" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL101" s="27" t="s">
         <v>280</v>
@@ -11424,16 +11421,16 @@
       </c>
       <c r="AO101" s="27"/>
       <c r="AQ101" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AY101" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB101" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="102" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="102" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>215</v>
       </c>
@@ -11447,16 +11444,16 @@
         <v>215</v>
       </c>
       <c r="E102" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F102" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G102" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H102" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -11502,7 +11499,7 @@
         <v>278</v>
       </c>
       <c r="AK102" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL102" s="27" t="s">
         <v>280</v>
@@ -11513,18 +11510,18 @@
       </c>
       <c r="AO102" s="27"/>
       <c r="AQ102" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AY102" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB102" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="103" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="103" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B103" s="4">
         <v>1</v>
@@ -11533,19 +11530,19 @@
         <v>191</v>
       </c>
       <c r="D103" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F103" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G103" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H103" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I103">
         <v>1</v>
@@ -11587,7 +11584,7 @@
         <v>278</v>
       </c>
       <c r="AK103" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL103" s="27" t="s">
         <v>280</v>
@@ -11598,16 +11595,16 @@
       </c>
       <c r="AO103" s="27"/>
       <c r="AQ103" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AY103" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB103" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="104" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="104" spans="1:54" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>218</v>
       </c>
@@ -11621,16 +11618,16 @@
         <v>218</v>
       </c>
       <c r="E104" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F104" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G104" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H104" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I104">
         <v>1</v>
@@ -11672,7 +11669,7 @@
         <v>278</v>
       </c>
       <c r="AK104" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AL104" s="27" t="s">
         <v>280</v>
@@ -11683,16 +11680,16 @@
       </c>
       <c r="AO104" s="27"/>
       <c r="AQ104" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AY104" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB104" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="105" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="105" spans="1:54" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>219</v>
       </c>
@@ -11722,7 +11719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:54" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:54" s="4" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>220</v>
       </c>
@@ -11772,7 +11769,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="107" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>225</v>
       </c>
@@ -11786,7 +11783,7 @@
         <v>225</v>
       </c>
       <c r="F107" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -11834,7 +11831,7 @@
         <v>2011</v>
       </c>
       <c r="AD107" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AF107" s="6" t="s">
         <v>228</v>
@@ -11866,25 +11863,25 @@
         <v>276</v>
       </c>
       <c r="AQ107" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR107" t="s">
         <v>270</v>
       </c>
       <c r="AV107" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AW107" t="s">
         <v>291</v>
       </c>
       <c r="AY107" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="BB107" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="108" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="108" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>230</v>
       </c>
@@ -11898,7 +11895,7 @@
         <v>230</v>
       </c>
       <c r="F108" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -11973,7 +11970,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="109" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:54" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>230</v>
       </c>
@@ -11987,7 +11984,7 @@
         <v>230</v>
       </c>
       <c r="F109" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -12035,10 +12032,10 @@
         <v>2025</v>
       </c>
       <c r="AD109" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AF109" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AG109" t="s">
         <v>232</v>
@@ -12065,7 +12062,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="110" spans="1:54" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>233</v>
       </c>
@@ -12079,10 +12076,10 @@
         <v>233</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F110" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G110" t="s">
         <v>315</v>
@@ -12136,7 +12133,7 @@
         <v>2015</v>
       </c>
       <c r="AD110" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AF110" s="6" t="s">
         <v>235</v>
@@ -12148,19 +12145,19 @@
         <v>1</v>
       </c>
       <c r="AI110" t="s">
+        <v>557</v>
+      </c>
+      <c r="AQ110" t="s">
+        <v>552</v>
+      </c>
+      <c r="AT110" t="s">
         <v>558</v>
       </c>
-      <c r="AQ110" t="s">
-        <v>553</v>
-      </c>
-      <c r="AT110" t="s">
+      <c r="BB110" t="s">
         <v>559</v>
       </c>
-      <c r="BB110" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="111" spans="1:54" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>233</v>
       </c>
@@ -12174,10 +12171,10 @@
         <v>233</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F111" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G111" t="s">
         <v>315</v>
@@ -12231,7 +12228,7 @@
         <v>2022</v>
       </c>
       <c r="AD111" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AF111" s="6" t="s">
         <v>235</v>
@@ -12243,19 +12240,19 @@
         <v>1</v>
       </c>
       <c r="AI111" t="s">
+        <v>557</v>
+      </c>
+      <c r="AQ111" t="s">
+        <v>552</v>
+      </c>
+      <c r="AT111" t="s">
         <v>558</v>
       </c>
-      <c r="AQ111" t="s">
-        <v>553</v>
-      </c>
-      <c r="AT111" t="s">
+      <c r="BB111" t="s">
         <v>559</v>
       </c>
-      <c r="BB111" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="112" spans="1:54" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:54" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>233</v>
       </c>
@@ -12269,10 +12266,10 @@
         <v>233</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F112" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G112" t="s">
         <v>315</v>
@@ -12326,10 +12323,10 @@
         <v>2025</v>
       </c>
       <c r="AD112" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AE112" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AF112" s="6" t="s">
         <v>235</v>
@@ -12341,19 +12338,19 @@
         <v>1</v>
       </c>
       <c r="AI112" t="s">
+        <v>557</v>
+      </c>
+      <c r="AQ112" t="s">
+        <v>552</v>
+      </c>
+      <c r="AT112" t="s">
         <v>558</v>
       </c>
-      <c r="AQ112" t="s">
-        <v>553</v>
-      </c>
-      <c r="AT112" t="s">
+      <c r="BB112" t="s">
         <v>559</v>
       </c>
-      <c r="BB112" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="113" spans="1:56" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>237</v>
       </c>
@@ -12367,10 +12364,10 @@
         <v>237</v>
       </c>
       <c r="F113" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H113" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I113">
         <v>1</v>
@@ -12409,12 +12406,12 @@
         <v>239</v>
       </c>
     </row>
-    <row r="114" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:56" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>240</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C114" t="s">
         <v>233</v>
@@ -12423,16 +12420,16 @@
         <v>240</v>
       </c>
       <c r="E114" t="s">
+        <v>646</v>
+      </c>
+      <c r="F114" t="s">
         <v>647</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="G114" s="6" t="s">
-        <v>649</v>
-      </c>
       <c r="H114" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I114">
         <v>1</v>
@@ -12441,7 +12438,7 @@
         <v>25</v>
       </c>
       <c r="K114" s="29" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="M114" t="s">
         <v>26</v>
@@ -12471,25 +12468,25 @@
         <v>241</v>
       </c>
       <c r="AJ114" t="s">
+        <v>639</v>
+      </c>
+      <c r="AK114" t="s">
         <v>640</v>
       </c>
-      <c r="AK114" t="s">
+      <c r="AL114" t="s">
         <v>641</v>
       </c>
-      <c r="AL114" t="s">
+      <c r="AM114" t="s">
         <v>642</v>
       </c>
-      <c r="AM114" t="s">
+      <c r="AO114" t="s">
         <v>643</v>
       </c>
-      <c r="AO114" t="s">
+      <c r="AP114" t="s">
         <v>644</v>
       </c>
-      <c r="AP114" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="115" spans="1:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:56" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>242</v>
       </c>
@@ -12503,13 +12500,13 @@
         <v>242</v>
       </c>
       <c r="F115" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G115" t="s">
         <v>315</v>
       </c>
       <c r="H115" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I115">
         <v>1</v>
@@ -12548,7 +12545,7 @@
         <v>2023</v>
       </c>
       <c r="AD115" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AF115" s="6" t="s">
         <v>243</v>
@@ -12560,7 +12557,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="116" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>244</v>
       </c>
@@ -12574,13 +12571,13 @@
         <v>244</v>
       </c>
       <c r="E116" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="F116" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G116" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -12601,7 +12598,7 @@
         <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="O116" t="s">
         <v>35</v>
@@ -12637,7 +12634,7 @@
         <v>2019</v>
       </c>
       <c r="AD116" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AE116" s="6"/>
       <c r="AG116" t="s">
@@ -12647,19 +12644,19 @@
         <v>1</v>
       </c>
       <c r="AJ116" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK116" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AR116" t="s">
         <v>270</v>
       </c>
       <c r="AY116" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="117" spans="1:56" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="117" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>244</v>
       </c>
@@ -12673,13 +12670,13 @@
         <v>244</v>
       </c>
       <c r="E117" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="F117" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G117" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -12700,7 +12697,7 @@
         <v>26</v>
       </c>
       <c r="N117" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="O117" t="s">
         <v>35</v>
@@ -12733,10 +12730,10 @@
         <v>2018</v>
       </c>
       <c r="AB117" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AD117" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AE117" s="6"/>
       <c r="AG117" t="s">
@@ -12746,10 +12743,10 @@
         <v>1</v>
       </c>
       <c r="AJ117" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK117" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AL117" t="s">
         <v>280</v>
@@ -12758,16 +12755,16 @@
         <v>276</v>
       </c>
       <c r="AQ117" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AR117" t="s">
         <v>270</v>
       </c>
       <c r="BB117" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="118" spans="1:56" ht="75" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="118" spans="1:56" ht="64" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>247</v>
       </c>
@@ -12781,10 +12778,10 @@
         <v>247</v>
       </c>
       <c r="E118" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F118" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -12844,13 +12841,13 @@
         <v>1</v>
       </c>
       <c r="AJ118" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK118" t="s">
         <v>275</v>
       </c>
       <c r="AL118" s="15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AP118" t="s">
         <v>276</v>
@@ -12859,19 +12856,19 @@
         <v>270</v>
       </c>
       <c r="AV118" s="29" t="s">
+        <v>659</v>
+      </c>
+      <c r="AW118" s="15" t="s">
         <v>660</v>
       </c>
-      <c r="AW118" s="15" t="s">
-        <v>661</v>
-      </c>
       <c r="AY118" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="BB118" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="119" spans="1:56" ht="75" x14ac:dyDescent="0.25">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="119" spans="1:56" ht="64" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>247</v>
       </c>
@@ -12885,13 +12882,13 @@
         <v>247</v>
       </c>
       <c r="E119" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F119" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G119" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -12942,7 +12939,7 @@
         <v>2024</v>
       </c>
       <c r="AB119" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AF119" s="6" t="s">
         <v>250</v>
@@ -12954,34 +12951,34 @@
         <v>1</v>
       </c>
       <c r="AJ119" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AK119" t="s">
         <v>275</v>
       </c>
       <c r="AL119" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="AP119" t="s">
         <v>658</v>
-      </c>
-      <c r="AP119" t="s">
-        <v>659</v>
       </c>
       <c r="AR119" t="s">
         <v>270</v>
       </c>
       <c r="AV119" s="29" t="s">
+        <v>659</v>
+      </c>
+      <c r="AW119" s="15" t="s">
         <v>660</v>
       </c>
-      <c r="AW119" s="15" t="s">
+      <c r="AY119" t="s">
         <v>661</v>
       </c>
-      <c r="AY119" t="s">
+      <c r="BB119" t="s">
         <v>662</v>
       </c>
-      <c r="BB119" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="120" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:56" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>252</v>
       </c>
@@ -13031,7 +13028,7 @@
       <c r="BB120" s="22"/>
       <c r="BD120" s="22"/>
     </row>
-    <row r="121" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>253</v>
       </c>
@@ -13066,7 +13063,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="122" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:56" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>255</v>
       </c>
@@ -13080,16 +13077,16 @@
         <v>255</v>
       </c>
       <c r="E122" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F122" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G122" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H122" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I122">
         <v>1</v>
@@ -13143,7 +13140,7 @@
         <v>2023</v>
       </c>
       <c r="AE122" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AF122" t="s">
         <v>258</v>
@@ -13156,28 +13153,28 @@
       </c>
       <c r="AI122" s="27"/>
       <c r="AJ122" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AK122" s="27" t="s">
         <v>275</v>
       </c>
       <c r="AL122" s="27" t="s">
+        <v>563</v>
+      </c>
+      <c r="AM122" t="s">
         <v>564</v>
       </c>
-      <c r="AM122" t="s">
+      <c r="AN122" s="27" t="s">
         <v>565</v>
-      </c>
-      <c r="AN122" s="27" t="s">
-        <v>566</v>
       </c>
       <c r="AP122" t="s">
         <v>279</v>
       </c>
       <c r="BB122" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="123" spans="1:56" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="123" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>260</v>
       </c>
@@ -13191,16 +13188,16 @@
         <v>260</v>
       </c>
       <c r="E123" t="s">
+        <v>613</v>
+      </c>
+      <c r="F123" t="s">
         <v>614</v>
       </c>
-      <c r="F123" t="s">
-        <v>615</v>
-      </c>
       <c r="G123" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H123" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I123">
         <v>1</v>
@@ -13283,7 +13280,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="124" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -13297,13 +13294,13 @@
         <v>263</v>
       </c>
       <c r="E124" t="s">
+        <v>615</v>
+      </c>
+      <c r="F124" t="s">
         <v>616</v>
       </c>
-      <c r="F124" t="s">
-        <v>617</v>
-      </c>
       <c r="H124" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I124">
         <v>1</v>
@@ -13321,7 +13318,7 @@
         <v>39</v>
       </c>
       <c r="N124" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="O124" t="s">
         <v>264</v>
@@ -13357,19 +13354,19 @@
         <v>275</v>
       </c>
       <c r="AL124" t="s">
+        <v>563</v>
+      </c>
+      <c r="AM124" t="s">
         <v>564</v>
       </c>
-      <c r="AM124" t="s">
+      <c r="AN124" t="s">
         <v>565</v>
-      </c>
-      <c r="AN124" t="s">
-        <v>566</v>
       </c>
       <c r="AP124" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="125" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:56" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>267</v>
       </c>
@@ -13383,10 +13380,10 @@
         <v>267</v>
       </c>
       <c r="F125" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H125" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I125">
         <v>1</v>
@@ -13449,21 +13446,21 @@
         <v>2023</v>
       </c>
       <c r="AD125" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AF125" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AG125" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="126" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>233</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C126" t="s">
         <v>233</v>
@@ -13478,7 +13475,7 @@
         <v>378</v>
       </c>
       <c r="H126" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I126">
         <v>1</v>
@@ -13508,18 +13505,18 @@
         <v>381</v>
       </c>
       <c r="AD126" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AF126" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="127" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="127" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>88</v>
       </c>
       <c r="B127" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C127" t="s">
         <v>88</v>
@@ -13534,7 +13531,7 @@
         <v>378</v>
       </c>
       <c r="H127" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I127">
         <v>1</v>
@@ -13567,18 +13564,18 @@
         <v>386</v>
       </c>
       <c r="AD127" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AF127" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="128" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="128" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>169</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C128" t="s">
         <v>169</v>
@@ -13593,7 +13590,7 @@
         <v>378</v>
       </c>
       <c r="H128" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I128">
         <v>1</v>
@@ -13632,15 +13629,15 @@
         <v>392</v>
       </c>
       <c r="AF128" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="129" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="129" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>88</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C129" t="s">
         <v>88</v>
@@ -13655,7 +13652,7 @@
         <v>378</v>
       </c>
       <c r="H129" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I129">
         <v>1</v>
@@ -13697,27 +13694,27 @@
         <v>398</v>
       </c>
     </row>
-    <row r="130" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
+        <v>247</v>
+      </c>
+      <c r="B130" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="C130" t="s">
+        <v>247</v>
+      </c>
+      <c r="D130" t="s">
         <v>400</v>
-      </c>
-      <c r="B130" s="22" t="s">
-        <v>577</v>
-      </c>
-      <c r="C130" t="s">
-        <v>400</v>
-      </c>
-      <c r="D130" t="s">
-        <v>401</v>
       </c>
       <c r="F130" t="s">
         <v>399</v>
       </c>
       <c r="G130" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H130" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I130">
         <v>1</v>
@@ -13726,7 +13723,7 @@
         <v>25</v>
       </c>
       <c r="K130" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M130" t="s">
         <v>26</v>
@@ -13735,13 +13732,13 @@
         <v>318</v>
       </c>
       <c r="O130" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T130" t="s">
+        <v>403</v>
+      </c>
+      <c r="U130" t="s">
         <v>404</v>
-      </c>
-      <c r="U130" t="s">
-        <v>405</v>
       </c>
       <c r="AA130">
         <v>2024</v>
@@ -13750,36 +13747,36 @@
         <v>2024</v>
       </c>
       <c r="AC130" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="AD130" t="s">
         <v>406</v>
       </c>
-      <c r="AD130" t="s">
-        <v>407</v>
-      </c>
       <c r="AF130" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="131" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="131" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>135</v>
       </c>
       <c r="B131" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C131" t="s">
         <v>135</v>
       </c>
       <c r="D131" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F131" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G131" t="s">
         <v>378</v>
       </c>
       <c r="H131" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I131">
         <v>1</v>
@@ -13797,10 +13794,10 @@
         <v>264</v>
       </c>
       <c r="T131" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="U131" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA131">
         <v>2023</v>
@@ -13812,33 +13809,33 @@
         <v>381</v>
       </c>
       <c r="AD131" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AF131" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="132" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="132" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>128</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C132" t="s">
         <v>128</v>
       </c>
       <c r="D132" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F132" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G132" t="s">
         <v>378</v>
       </c>
       <c r="H132" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I132">
         <v>1</v>
@@ -13856,10 +13853,10 @@
         <v>310</v>
       </c>
       <c r="T132" t="s">
+        <v>413</v>
+      </c>
+      <c r="U132" t="s">
         <v>414</v>
-      </c>
-      <c r="U132" t="s">
-        <v>415</v>
       </c>
       <c r="AA132">
         <v>2021</v>
@@ -13868,36 +13865,36 @@
         <v>2021</v>
       </c>
       <c r="AC132" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="AD132" t="s">
         <v>416</v>
       </c>
-      <c r="AD132" t="s">
-        <v>417</v>
-      </c>
       <c r="AF132" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="133" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="133" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>128</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C133" t="s">
         <v>128</v>
       </c>
       <c r="D133" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F133" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G133" t="s">
         <v>378</v>
       </c>
       <c r="H133" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I133">
         <v>1</v>
@@ -13906,7 +13903,7 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M133" t="s">
         <v>26</v>
@@ -13918,7 +13915,7 @@
         <v>310</v>
       </c>
       <c r="T133" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="U133" t="s">
         <v>385</v>
@@ -13933,33 +13930,33 @@
         <v>269</v>
       </c>
       <c r="AD133" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AF133" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="134" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="134" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>83</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C134" t="s">
         <v>83</v>
       </c>
       <c r="D134" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F134" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G134" t="s">
         <v>315</v>
       </c>
       <c r="H134" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I134">
         <v>1</v>
@@ -13968,7 +13965,7 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M134" t="s">
         <v>26</v>
@@ -13980,7 +13977,7 @@
         <v>35</v>
       </c>
       <c r="T134" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="U134" t="s">
         <v>385</v>
@@ -13992,36 +13989,36 @@
         <v>2021</v>
       </c>
       <c r="AC134" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="AD134" t="s">
         <v>425</v>
       </c>
-      <c r="AD134" t="s">
-        <v>426</v>
-      </c>
       <c r="AF134" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="135" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="135" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>83</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C135" t="s">
         <v>83</v>
       </c>
       <c r="D135" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F135" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G135" t="s">
         <v>315</v>
       </c>
       <c r="H135" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I135">
         <v>1</v>
@@ -14030,7 +14027,7 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M135" t="s">
         <v>39</v>
@@ -14042,10 +14039,10 @@
         <v>35</v>
       </c>
       <c r="T135" t="s">
+        <v>428</v>
+      </c>
+      <c r="U135" t="s">
         <v>429</v>
-      </c>
-      <c r="U135" t="s">
-        <v>430</v>
       </c>
       <c r="AA135">
         <v>2023</v>
@@ -14057,33 +14054,33 @@
         <v>381</v>
       </c>
       <c r="AD135" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AF135" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="136" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="136" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>83</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C136" t="s">
         <v>83</v>
       </c>
       <c r="D136" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F136" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G136" t="s">
         <v>315</v>
       </c>
       <c r="H136" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="I136">
         <v>1</v>
@@ -14092,7 +14089,7 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M136" t="s">
         <v>39</v>
@@ -14104,10 +14101,10 @@
         <v>35</v>
       </c>
       <c r="T136" t="s">
+        <v>432</v>
+      </c>
+      <c r="U136" t="s">
         <v>433</v>
-      </c>
-      <c r="U136" t="s">
-        <v>434</v>
       </c>
       <c r="AA136">
         <v>2023</v>
@@ -14116,36 +14113,36 @@
         <v>2023</v>
       </c>
       <c r="AC136" s="25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AD136" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AF136" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="137" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="137" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>169</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C137" t="s">
         <v>169</v>
       </c>
       <c r="D137" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F137" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G137" t="s">
         <v>315</v>
       </c>
       <c r="H137" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I137">
         <v>1</v>
@@ -14163,13 +14160,13 @@
         <v>318</v>
       </c>
       <c r="O137" t="s">
+        <v>436</v>
+      </c>
+      <c r="T137" t="s">
         <v>437</v>
       </c>
-      <c r="T137" t="s">
+      <c r="U137" t="s">
         <v>438</v>
-      </c>
-      <c r="U137" t="s">
-        <v>439</v>
       </c>
       <c r="AA137">
         <v>2020</v>
@@ -14178,36 +14175,36 @@
         <v>2020</v>
       </c>
       <c r="AC137" s="24" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AD137" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AF137" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="138" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="138" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>20</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
       </c>
       <c r="D138" t="s">
+        <v>441</v>
+      </c>
+      <c r="F138" t="s">
+        <v>440</v>
+      </c>
+      <c r="G138" t="s">
         <v>442</v>
       </c>
-      <c r="F138" t="s">
-        <v>441</v>
-      </c>
-      <c r="G138" t="s">
-        <v>443</v>
-      </c>
       <c r="H138" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I138">
         <v>1</v>
@@ -14225,13 +14222,13 @@
         <v>318</v>
       </c>
       <c r="O138" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T138" t="s">
+        <v>443</v>
+      </c>
+      <c r="U138" t="s">
         <v>444</v>
-      </c>
-      <c r="U138" t="s">
-        <v>445</v>
       </c>
       <c r="AA138">
         <v>2019</v>
@@ -14243,33 +14240,33 @@
         <v>381</v>
       </c>
       <c r="AD138" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AF138" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="139" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="139" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>20</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F139" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G139" t="s">
         <v>315</v>
       </c>
       <c r="H139" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -14287,13 +14284,13 @@
         <v>318</v>
       </c>
       <c r="O139" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T139" t="s">
+        <v>447</v>
+      </c>
+      <c r="U139" t="s">
         <v>448</v>
-      </c>
-      <c r="U139" t="s">
-        <v>449</v>
       </c>
       <c r="AA139">
         <v>2022</v>
@@ -14305,33 +14302,33 @@
         <v>381</v>
       </c>
       <c r="AD139" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AF139" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="140" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="140" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>88</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C140" t="s">
         <v>88</v>
       </c>
       <c r="D140" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F140" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G140" t="s">
         <v>315</v>
       </c>
       <c r="H140" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -14349,13 +14346,13 @@
         <v>318</v>
       </c>
       <c r="O140" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T140" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="U140" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AA140">
         <v>2022</v>
@@ -14364,36 +14361,36 @@
         <v>2022</v>
       </c>
       <c r="AC140" s="25" t="s">
+        <v>451</v>
+      </c>
+      <c r="AD140" t="s">
         <v>452</v>
       </c>
-      <c r="AD140" t="s">
-        <v>453</v>
-      </c>
       <c r="AF140" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="141" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="141" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>135</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C141" t="s">
         <v>135</v>
       </c>
       <c r="D141" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F141" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G141" t="s">
         <v>315</v>
       </c>
       <c r="H141" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I141">
         <v>1</v>
@@ -14402,7 +14399,7 @@
         <v>25</v>
       </c>
       <c r="K141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M141" t="s">
         <v>26</v>
@@ -14414,10 +14411,10 @@
         <v>264</v>
       </c>
       <c r="T141" t="s">
+        <v>455</v>
+      </c>
+      <c r="U141" t="s">
         <v>456</v>
-      </c>
-      <c r="U141" t="s">
-        <v>457</v>
       </c>
       <c r="AA141">
         <v>2024</v>
@@ -14426,36 +14423,36 @@
         <v>2024</v>
       </c>
       <c r="AC141" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="AD141" t="s">
         <v>458</v>
       </c>
-      <c r="AD141" t="s">
-        <v>459</v>
-      </c>
       <c r="AF141" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="142" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="142" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>169</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C142" t="s">
         <v>169</v>
       </c>
       <c r="D142" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F142" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G142" t="s">
         <v>315</v>
       </c>
       <c r="H142" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -14464,7 +14461,7 @@
         <v>25</v>
       </c>
       <c r="K142" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M142" t="s">
         <v>26</v>
@@ -14473,13 +14470,13 @@
         <v>318</v>
       </c>
       <c r="O142" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T142" t="s">
+        <v>462</v>
+      </c>
+      <c r="U142" t="s">
         <v>463</v>
-      </c>
-      <c r="U142" t="s">
-        <v>464</v>
       </c>
       <c r="AA142">
         <v>2024</v>
@@ -14488,36 +14485,36 @@
         <v>2024</v>
       </c>
       <c r="AC142" s="25" t="s">
+        <v>464</v>
+      </c>
+      <c r="AD142" t="s">
         <v>465</v>
       </c>
-      <c r="AD142" t="s">
+      <c r="AF142" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="143" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>247</v>
+      </c>
+      <c r="B143" s="22" t="s">
+        <v>576</v>
+      </c>
+      <c r="C143" t="s">
+        <v>247</v>
+      </c>
+      <c r="D143" t="s">
         <v>466</v>
       </c>
-      <c r="AF142" t="s">
+      <c r="F143" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="143" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>400</v>
-      </c>
-      <c r="B143" s="22" t="s">
-        <v>577</v>
-      </c>
-      <c r="C143" t="s">
-        <v>400</v>
-      </c>
-      <c r="D143" t="s">
+      <c r="G143" t="s">
         <v>467</v>
       </c>
-      <c r="F143" t="s">
-        <v>467</v>
-      </c>
-      <c r="G143" t="s">
-        <v>468</v>
-      </c>
       <c r="H143" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -14526,7 +14523,7 @@
         <v>25</v>
       </c>
       <c r="K143" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="M143" t="s">
         <v>26</v>
@@ -14538,10 +14535,10 @@
         <v>35</v>
       </c>
       <c r="T143" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="U143" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AA143">
         <v>2018</v>
@@ -14550,36 +14547,36 @@
         <v>2018</v>
       </c>
       <c r="AC143" s="24" t="s">
+        <v>470</v>
+      </c>
+      <c r="AD143" t="s">
         <v>471</v>
       </c>
-      <c r="AD143" t="s">
-        <v>472</v>
-      </c>
       <c r="AF143" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="144" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="144" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>129</v>
       </c>
       <c r="B144" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C144" t="s">
         <v>129</v>
       </c>
       <c r="D144" t="s">
+        <v>472</v>
+      </c>
+      <c r="F144" t="s">
+        <v>472</v>
+      </c>
+      <c r="G144" t="s">
         <v>473</v>
       </c>
-      <c r="F144" t="s">
-        <v>473</v>
-      </c>
-      <c r="G144" t="s">
-        <v>474</v>
-      </c>
       <c r="H144" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -14588,7 +14585,7 @@
         <v>25</v>
       </c>
       <c r="K144" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="M144" t="s">
         <v>26</v>
@@ -14597,13 +14594,13 @@
         <v>318</v>
       </c>
       <c r="O144" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T144" t="s">
+        <v>475</v>
+      </c>
+      <c r="U144" t="s">
         <v>476</v>
-      </c>
-      <c r="U144" t="s">
-        <v>477</v>
       </c>
       <c r="AA144">
         <v>2024</v>
@@ -14612,39 +14609,39 @@
         <v>2024</v>
       </c>
       <c r="AC144" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AD144" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AF144" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="145" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="145" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>169</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C145" t="s">
         <v>169</v>
       </c>
       <c r="D145" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E145" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F145" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G145" t="s">
         <v>315</v>
       </c>
       <c r="H145" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -14653,7 +14650,7 @@
         <v>25</v>
       </c>
       <c r="K145" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M145" t="s">
         <v>26</v>
@@ -14662,13 +14659,13 @@
         <v>318</v>
       </c>
       <c r="O145" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T145" t="s">
+        <v>479</v>
+      </c>
+      <c r="U145" t="s">
         <v>480</v>
-      </c>
-      <c r="U145" t="s">
-        <v>481</v>
       </c>
       <c r="AA145">
         <v>2021</v>
@@ -14677,36 +14674,36 @@
         <v>2021</v>
       </c>
       <c r="AC145" s="24" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AD145" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AF145" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="146" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="146" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>20</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C146" t="s">
         <v>20</v>
       </c>
       <c r="D146" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F146" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G146" t="s">
         <v>315</v>
       </c>
       <c r="H146" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -14724,13 +14721,13 @@
         <v>318</v>
       </c>
       <c r="O146" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T146" t="s">
+        <v>482</v>
+      </c>
+      <c r="U146" t="s">
         <v>483</v>
-      </c>
-      <c r="U146" t="s">
-        <v>484</v>
       </c>
       <c r="AA146">
         <v>2021</v>
@@ -14739,36 +14736,36 @@
         <v>2021</v>
       </c>
       <c r="AC146" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AD146" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AF146" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="147" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="147" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>47</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C147" t="s">
         <v>47</v>
       </c>
       <c r="D147" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F147" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G147" t="s">
         <v>315</v>
       </c>
       <c r="H147" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -14777,7 +14774,7 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M147" t="s">
         <v>26</v>
@@ -14786,13 +14783,13 @@
         <v>318</v>
       </c>
       <c r="O147" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T147" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="U147" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AA147">
         <v>2024</v>
@@ -14801,36 +14798,36 @@
         <v>2024</v>
       </c>
       <c r="AC147" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AD147" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AF147" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="148" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="148" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>20</v>
       </c>
       <c r="B148" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C148" t="s">
         <v>20</v>
       </c>
       <c r="D148" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F148" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G148" t="s">
         <v>315</v>
       </c>
       <c r="H148" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -14839,7 +14836,7 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M148" t="s">
         <v>26</v>
@@ -14848,13 +14845,13 @@
         <v>318</v>
       </c>
       <c r="O148" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T148" t="s">
         <v>384</v>
       </c>
       <c r="U148" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AA148">
         <v>2019</v>
@@ -14863,39 +14860,39 @@
         <v>2019</v>
       </c>
       <c r="AC148" s="25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AD148" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AF148" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="149" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="149" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>169</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C149" t="s">
         <v>169</v>
       </c>
       <c r="D149" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E149" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F149" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G149" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H149" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -14904,7 +14901,7 @@
         <v>25</v>
       </c>
       <c r="K149" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M149" t="s">
         <v>26</v>
@@ -14913,13 +14910,13 @@
         <v>318</v>
       </c>
       <c r="O149" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T149" t="s">
+        <v>494</v>
+      </c>
+      <c r="U149" t="s">
         <v>495</v>
-      </c>
-      <c r="U149" t="s">
-        <v>496</v>
       </c>
       <c r="AA149">
         <v>2023</v>
@@ -14931,33 +14928,33 @@
         <v>381</v>
       </c>
       <c r="AD149" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AF149" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="150" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="150" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>20</v>
       </c>
       <c r="B150" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C150" t="s">
         <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F150" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G150" t="s">
         <v>315</v>
       </c>
       <c r="H150" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -14966,7 +14963,7 @@
         <v>25</v>
       </c>
       <c r="K150" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M150" t="s">
         <v>26</v>
@@ -14975,13 +14972,13 @@
         <v>318</v>
       </c>
       <c r="O150" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="T150" t="s">
+        <v>497</v>
+      </c>
+      <c r="U150" t="s">
         <v>498</v>
-      </c>
-      <c r="U150" t="s">
-        <v>499</v>
       </c>
       <c r="AA150">
         <v>2019</v>
@@ -14990,36 +14987,36 @@
         <v>2019</v>
       </c>
       <c r="AC150" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AD150" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AF150" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="151" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="151" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>88</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C151" t="s">
         <v>88</v>
       </c>
       <c r="D151" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F151" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G151" t="s">
         <v>315</v>
       </c>
       <c r="H151" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -15028,7 +15025,7 @@
         <v>25</v>
       </c>
       <c r="K151" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M151" t="s">
         <v>26</v>
@@ -15037,13 +15034,13 @@
         <v>318</v>
       </c>
       <c r="O151" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T151" t="s">
+        <v>500</v>
+      </c>
+      <c r="U151" t="s">
         <v>501</v>
-      </c>
-      <c r="U151" t="s">
-        <v>502</v>
       </c>
       <c r="AA151">
         <v>2023</v>
@@ -15052,36 +15049,36 @@
         <v>2023</v>
       </c>
       <c r="AC151" s="24" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AD151" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AF151" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="152" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="152" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>78</v>
       </c>
       <c r="B152" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C152" t="s">
         <v>78</v>
       </c>
       <c r="D152" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F152" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G152" t="s">
         <v>315</v>
       </c>
       <c r="H152" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I152">
         <v>1</v>
@@ -15090,7 +15087,7 @@
         <v>25</v>
       </c>
       <c r="K152" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M152" t="s">
         <v>26</v>
@@ -15099,13 +15096,13 @@
         <v>318</v>
       </c>
       <c r="O152" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="T152" t="s">
+        <v>506</v>
+      </c>
+      <c r="U152" t="s">
         <v>507</v>
-      </c>
-      <c r="U152" t="s">
-        <v>508</v>
       </c>
       <c r="AA152">
         <v>2021</v>
@@ -15117,36 +15114,36 @@
         <v>381</v>
       </c>
       <c r="AD152" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AF152" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="153" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="153" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>78</v>
       </c>
       <c r="B153" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C153" t="s">
         <v>78</v>
       </c>
       <c r="D153" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E153" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="F153" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G153" t="s">
         <v>315</v>
       </c>
       <c r="H153" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="I153">
         <v>1</v>
@@ -15155,7 +15152,7 @@
         <v>25</v>
       </c>
       <c r="K153" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M153" t="s">
         <v>26</v>
@@ -15167,10 +15164,10 @@
         <v>35</v>
       </c>
       <c r="T153" t="s">
+        <v>509</v>
+      </c>
+      <c r="U153" t="s">
         <v>510</v>
-      </c>
-      <c r="U153" t="s">
-        <v>511</v>
       </c>
       <c r="AA153">
         <v>2022</v>
@@ -15182,16 +15179,16 @@
         <v>381</v>
       </c>
       <c r="AD153" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AF153" t="s">
+        <v>752</v>
+      </c>
+      <c r="AG153" s="15" t="s">
         <v>753</v>
       </c>
-      <c r="AG153" s="15" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="154" spans="1:33" ht="13.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:33" ht="13.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B154" s="22"/>
       <c r="N154" s="23"/>
       <c r="AC154" s="24"/>

--- a/scripts/Quality_parameters.xlsx
+++ b/scripts/Quality_parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/localadmin/Repos/Website_Open_Topography_EU/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF5230D-0800-5A41-AD39-C9BE0B93F804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8814FA7C-CB6D-A94E-947A-A33B7841FFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
   </bookViews>
@@ -13457,7 +13457,7 @@
     </row>
     <row r="126" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>233</v>
+        <v>377</v>
       </c>
       <c r="B126" s="22" t="s">
         <v>576</v>
@@ -13513,7 +13513,7 @@
     </row>
     <row r="127" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>88</v>
+        <v>383</v>
       </c>
       <c r="B127" s="22" t="s">
         <v>576</v>
@@ -13572,7 +13572,7 @@
     </row>
     <row r="128" spans="1:56" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>169</v>
+        <v>388</v>
       </c>
       <c r="B128" s="22" t="s">
         <v>576</v>
@@ -13634,7 +13634,7 @@
     </row>
     <row r="129" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>88</v>
+        <v>394</v>
       </c>
       <c r="B129" s="22" t="s">
         <v>576</v>
@@ -13696,7 +13696,7 @@
     </row>
     <row r="130" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>247</v>
+        <v>400</v>
       </c>
       <c r="B130" s="22" t="s">
         <v>576</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="131" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>135</v>
+        <v>408</v>
       </c>
       <c r="B131" s="22" t="s">
         <v>576</v>
@@ -13817,7 +13817,7 @@
     </row>
     <row r="132" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>128</v>
+        <v>412</v>
       </c>
       <c r="B132" s="22" t="s">
         <v>576</v>
@@ -13876,7 +13876,7 @@
     </row>
     <row r="133" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>128</v>
+        <v>412</v>
       </c>
       <c r="B133" s="22" t="s">
         <v>576</v>
@@ -13938,7 +13938,7 @@
     </row>
     <row r="134" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="B134" s="22" t="s">
         <v>576</v>
@@ -14000,7 +14000,7 @@
     </row>
     <row r="135" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="B135" s="22" t="s">
         <v>576</v>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="136" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>83</v>
+        <v>421</v>
       </c>
       <c r="B136" s="22" t="s">
         <v>576</v>
@@ -14124,7 +14124,7 @@
     </row>
     <row r="137" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>169</v>
+        <v>435</v>
       </c>
       <c r="B137" s="22" t="s">
         <v>576</v>
@@ -14186,7 +14186,7 @@
     </row>
     <row r="138" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="B138" s="22" t="s">
         <v>576</v>
@@ -14248,7 +14248,7 @@
     </row>
     <row r="139" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="B139" s="22" t="s">
         <v>576</v>
@@ -14310,7 +14310,7 @@
     </row>
     <row r="140" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>88</v>
+        <v>450</v>
       </c>
       <c r="B140" s="22" t="s">
         <v>576</v>
@@ -14372,7 +14372,7 @@
     </row>
     <row r="141" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>135</v>
+        <v>453</v>
       </c>
       <c r="B141" s="22" t="s">
         <v>576</v>
@@ -14434,7 +14434,7 @@
     </row>
     <row r="142" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>169</v>
+        <v>460</v>
       </c>
       <c r="B142" s="22" t="s">
         <v>576</v>
@@ -14496,7 +14496,7 @@
     </row>
     <row r="143" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>247</v>
+        <v>466</v>
       </c>
       <c r="B143" s="22" t="s">
         <v>576</v>
@@ -14558,7 +14558,7 @@
     </row>
     <row r="144" spans="1:32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>129</v>
+        <v>472</v>
       </c>
       <c r="B144" s="22" t="s">
         <v>576</v>
@@ -14620,7 +14620,7 @@
     </row>
     <row r="145" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>169</v>
+        <v>478</v>
       </c>
       <c r="B145" s="22" t="s">
         <v>576</v>
@@ -14685,7 +14685,7 @@
     </row>
     <row r="146" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>441</v>
       </c>
       <c r="B146" s="22" t="s">
         <v>576</v>
@@ -14747,7 +14747,7 @@
     </row>
     <row r="147" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>47</v>
+        <v>485</v>
       </c>
       <c r="B147" s="22" t="s">
         <v>576</v>
@@ -14809,7 +14809,7 @@
     </row>
     <row r="148" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>20</v>
+        <v>489</v>
       </c>
       <c r="B148" s="22" t="s">
         <v>576</v>
@@ -14871,7 +14871,7 @@
     </row>
     <row r="149" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>169</v>
+        <v>460</v>
       </c>
       <c r="B149" s="22" t="s">
         <v>576</v>
@@ -14936,7 +14936,7 @@
     </row>
     <row r="150" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>20</v>
+        <v>496</v>
       </c>
       <c r="B150" s="22" t="s">
         <v>576</v>
@@ -14998,7 +14998,7 @@
     </row>
     <row r="151" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>88</v>
+        <v>499</v>
       </c>
       <c r="B151" s="22" t="s">
         <v>576</v>
@@ -15060,7 +15060,7 @@
     </row>
     <row r="152" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="B152" s="22" t="s">
         <v>576</v>
@@ -15122,7 +15122,7 @@
     </row>
     <row r="153" spans="1:33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>78</v>
+        <v>508</v>
       </c>
       <c r="B153" s="22" t="s">
         <v>576</v>

--- a/scripts/Quality_parameters.xlsx
+++ b/scripts/Quality_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/localadmin/Repos/Website_Open_Topography_EU/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8814FA7C-CB6D-A94E-947A-A33B7841FFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E9DC6B-C4F2-DE4A-ACDA-46845B25E36A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
   </bookViews>
@@ -2755,7 +2755,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2794,6 +2794,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFDAEEF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2842,7 +2848,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2904,6 +2910,8 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -5893,47 +5901,47 @@
         <v>519</v>
       </c>
     </row>
-    <row r="35" spans="1:63" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:63" s="33" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="4">
+      <c r="B35" s="34">
         <v>2</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="33" t="s">
         <v>618</v>
       </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="s">
+      <c r="I35" s="33">
+        <v>1</v>
+      </c>
+      <c r="AJ35" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="AK35" t="s">
+      <c r="AK35" s="33" t="s">
         <v>515</v>
       </c>
-      <c r="AN35" t="s">
+      <c r="AN35" s="33" t="s">
         <v>516</v>
       </c>
-      <c r="AP35" t="s">
+      <c r="AP35" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="AQ35" t="s">
+      <c r="AQ35" s="33" t="s">
         <v>517</v>
       </c>
-      <c r="AR35" t="s">
+      <c r="AR35" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="AY35" t="s">
+      <c r="AY35" s="33" t="s">
         <v>518</v>
       </c>
-      <c r="BB35" t="s">
+      <c r="BB35" s="33" t="s">
         <v>519</v>
       </c>
     </row>
@@ -8722,7 +8730,7 @@
         <v>576</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D72" t="s">
         <v>150</v>

--- a/scripts/Quality_parameters.xlsx
+++ b/scripts/Quality_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daan\Documents\GitHub\Website_Open_Topography_EU\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC9B181A-FCE0-47C8-8302-AB5A3636DD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234EB91C-85E7-4D53-B70C-E5E6D4D293BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{4BC1C8BB-35EF-4D62-B165-EB1ACD4AD7A7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2506" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2508" uniqueCount="807">
   <si>
     <t>ADM</t>
   </si>
@@ -2651,12 +2651,15 @@
     <t xml:space="preserve">In Germany, the availability of point cloud datasets is divided between the federal government and the Bundesländer (federal states), reflecting a distinction between national and regional scopes. Several datasets were identified in Germany that are available as open-access point cloud data. All elevation or point cloud datasets are acquired using the ETRS89 / UTM Zone 32 or 33 coordinate systems. For vertical reference, data acquired before 2017 use the DHHN92 height system, while data acquired from 2017 onwards use the DHHN2016 height system. Please note that the Digital Twin Germany (DigiZ-DE) as given as the main national lidar point cloud dataset, will not replace the current ATKIS DGM1,  but is intended to update and refine the existing entry “ATKIS DGM1”. As the dataset is not yet published, the only reference to it is on the documentation page. Our team is in close contact with the BKG to update the portal accordingly when the dataset is published. 
 </t>
   </si>
+  <si>
+    <t>ACT - Kadaster Lëtzebuerg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2809,6 +2812,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -2907,7 +2916,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2971,6 +2980,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Goed" xfId="1" builtinId="26"/>
@@ -9170,6 +9180,9 @@
       <c r="F75" t="s">
         <v>795</v>
       </c>
+      <c r="G75" s="33" t="s">
+        <v>806</v>
+      </c>
       <c r="H75" t="s">
         <v>8</v>
       </c>
@@ -9208,16 +9221,16 @@
       <c r="AB75">
         <v>2024</v>
       </c>
-      <c r="AD75" s="34" t="s">
+      <c r="AD75" s="35" t="s">
         <v>793</v>
       </c>
-      <c r="AE75" s="34" t="s">
+      <c r="AE75" s="35" t="s">
         <v>797</v>
       </c>
-      <c r="AF75" s="34" t="s">
+      <c r="AF75" s="35" t="s">
         <v>794</v>
       </c>
-      <c r="AH75" s="33" t="s">
+      <c r="AH75" s="34" t="s">
         <v>791</v>
       </c>
       <c r="AI75" s="2" t="s">
@@ -9277,6 +9290,9 @@
       <c r="F76" t="s">
         <v>597</v>
       </c>
+      <c r="G76" s="33" t="s">
+        <v>806</v>
+      </c>
       <c r="H76" t="s">
         <v>8</v>
       </c>
@@ -9319,10 +9335,10 @@
       <c r="AB76">
         <v>2019</v>
       </c>
-      <c r="AD76" s="34" t="s">
+      <c r="AD76" s="35" t="s">
         <v>793</v>
       </c>
-      <c r="AE76" s="34"/>
+      <c r="AE76" s="35"/>
       <c r="AH76" t="s">
         <v>159</v>
       </c>
